--- a/existing.xlsx
+++ b/existing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46">
   <si>
     <t>Link</t>
   </si>
@@ -120,6 +120,9 @@
     <t>https://maps.app.goo.gl/skwpSLYRmqdiQ5GR8</t>
   </si>
   <si>
+    <t>google map  (tutup)</t>
+  </si>
+  <si>
     <t>02126890577</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
   </si>
   <si>
     <t>https://www.instagram.com/soto_bangkong_semarang/</t>
+  </si>
+  <si>
+    <t>instagram (tutup)</t>
   </si>
   <si>
     <t>pusat? abandon</t>
@@ -1157,7 +1163,7 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="50.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="16.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="19.2857142857143" style="1" customWidth="1"/>
     <col min="4" max="4" width="54.8571428571429" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.1428571428571" customWidth="1"/>
@@ -1375,55 +1381,55 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
